--- a/US/cpi_median_trim_weights.xlsx
+++ b/US/cpi_median_trim_weights.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josesilva/Documents/Brasil-Economics-app/data-us/cpi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10E42DE-97AA-4343-9E45-C4CC7ADD76BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E910F23-FF1A-1940-B023-27AF7DF1FC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -533,7 +533,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,13 +551,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -604,7 +597,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3736,86 +3729,86 @@
         <v>7.0919999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="35" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="3">
         <v>1.8109999999999999</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="3">
         <v>1.7709999999999999</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="3">
         <v>1.7649999999999999</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="3">
         <v>1.716</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <v>1.7769999999999999</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="3">
         <v>1.7430000000000001</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="3">
         <v>1.8520000000000001</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="3">
         <v>2.0219999999999998</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="3">
         <v>2.0230000000000001</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="3">
         <v>1.996</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="3">
         <v>2.2719999999999998</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="3">
         <v>2.278</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="3">
         <v>2.0270000000000001</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="3">
         <v>2.0430000000000001</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="3">
         <v>2.0329999999999999</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="3">
         <v>1.986</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="3">
         <v>1.8640000000000001</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="3">
         <v>1.8320000000000001</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="3">
         <v>1.925</v>
       </c>
-      <c r="V35">
+      <c r="V35" s="3">
         <v>1.972</v>
       </c>
-      <c r="W35">
+      <c r="W35" s="3">
         <v>2.153</v>
       </c>
-      <c r="X35">
+      <c r="X35" s="3">
         <v>2.347</v>
       </c>
-      <c r="Y35">
+      <c r="Y35" s="3">
         <v>2.1930000000000001</v>
       </c>
-      <c r="Z35">
+      <c r="Z35" s="3">
         <v>2.3380000000000001</v>
       </c>
-      <c r="AA35">
+      <c r="AA35" s="3">
         <v>2.2730000000000001</v>
       </c>
     </row>
@@ -4841,11 +4834,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA46" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA46">
-      <sortCondition ref="B1:B46"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8181,501 +8169,501 @@
         <v>0.50800000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+    <row r="42" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="3">
         <v>1.8109999999999999</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="3">
         <v>1.7709999999999999</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="3">
         <v>1.7649999999999999</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="3">
         <v>1.716</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <v>1.7769999999999999</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="3">
         <v>1.7430000000000001</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="3">
         <v>1.8520000000000001</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="3">
         <v>2.0219999999999998</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="3">
         <v>2.0230000000000001</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="3">
         <v>1.996</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="3">
         <v>2.2719999999999998</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="3">
         <v>2.278</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="3">
         <v>2.0270000000000001</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="3">
         <v>2.0430000000000001</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="3">
         <v>2.0329999999999999</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="3">
         <v>1.986</v>
       </c>
-      <c r="S42">
+      <c r="S42" s="3">
         <v>1.8640000000000001</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="3">
         <v>1.8320000000000001</v>
       </c>
-      <c r="U42">
+      <c r="U42" s="3">
         <v>1.925</v>
       </c>
-      <c r="V42">
+      <c r="V42" s="3">
         <v>1.972</v>
       </c>
-      <c r="W42">
+      <c r="W42" s="3">
         <v>2.153</v>
       </c>
-      <c r="X42">
+      <c r="X42" s="3">
         <v>2.347</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" s="3">
         <v>2.1930000000000001</v>
       </c>
-      <c r="Z42">
+      <c r="Z42" s="3">
         <v>2.3380000000000001</v>
       </c>
-      <c r="AA42">
+      <c r="AA42" s="3">
         <v>2.2730000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+    <row r="43" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
         <v>0.70599999999999996</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="3">
         <v>0.68</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="3">
         <v>0.68</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="3">
         <v>0.65800000000000003</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="3">
         <v>0.71</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="3">
         <v>0.70799999999999996</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="3">
         <v>0.63900000000000001</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="3">
         <v>0.65100000000000002</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="3">
         <v>0.68799999999999994</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="3">
         <v>0.67100000000000004</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="3">
         <v>0.65600000000000003</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="3">
         <v>0.64600000000000002</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="3">
         <v>0.72699999999999998</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="3">
         <v>0.72399999999999998</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="3">
         <v>0.71699999999999997</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="3">
         <v>0.7</v>
       </c>
-      <c r="S43">
+      <c r="S43" s="3">
         <v>0.70399999999999996</v>
       </c>
-      <c r="T43">
+      <c r="T43" s="3">
         <v>0.68799999999999994</v>
       </c>
-      <c r="U43">
+      <c r="U43" s="3">
         <v>0.68899999999999995</v>
       </c>
-      <c r="V43">
+      <c r="V43" s="3">
         <v>0.67800000000000005</v>
       </c>
-      <c r="W43">
+      <c r="W43" s="3">
         <v>0.64800000000000002</v>
       </c>
-      <c r="X43">
+      <c r="X43" s="3">
         <v>0.59899999999999998</v>
       </c>
-      <c r="Y43">
+      <c r="Y43" s="3">
         <v>0.66600000000000004</v>
       </c>
-      <c r="Z43">
+      <c r="Z43" s="3">
         <v>0.64900000000000002</v>
       </c>
-      <c r="AA43">
+      <c r="AA43" s="3">
         <v>0.67400000000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="44" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="3">
         <v>0.90100000000000002</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="3">
         <v>0.89700000000000002</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="3">
         <v>0.65</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="3">
         <v>0.65200000000000002</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <v>0.67500000000000004</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="3">
         <v>0.67700000000000005</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="3">
         <v>0.629</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="3">
         <v>0.64700000000000002</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="3">
         <v>0.64200000000000002</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="3">
         <v>0.63800000000000001</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="3">
         <v>0.63300000000000001</v>
       </c>
-      <c r="N44">
+      <c r="N44" s="3">
         <v>0.63300000000000001</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="3">
         <v>0.63300000000000001</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="3">
         <v>0.63800000000000001</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="3">
         <v>0.61</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="3">
         <v>0.61</v>
       </c>
-      <c r="S44">
+      <c r="S44" s="3">
         <v>0.623</v>
       </c>
-      <c r="T44">
+      <c r="T44" s="3">
         <v>0.63300000000000001</v>
       </c>
-      <c r="U44">
+      <c r="U44" s="3">
         <v>0.66600000000000004</v>
       </c>
-      <c r="V44">
+      <c r="V44" s="3">
         <v>0.69399999999999995</v>
       </c>
-      <c r="W44">
+      <c r="W44" s="3">
         <v>0.54600000000000004</v>
       </c>
-      <c r="X44">
+      <c r="X44" s="3">
         <v>0.60699999999999998</v>
       </c>
-      <c r="Y44">
+      <c r="Y44" s="3">
         <v>0.629</v>
       </c>
-      <c r="Z44">
+      <c r="Z44" s="3">
         <v>0.65900000000000003</v>
       </c>
-      <c r="AA44">
+      <c r="AA44" s="3">
         <v>0.67600000000000005</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+    <row r="45" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="3">
         <v>0.27600000000000002</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="3">
         <v>0.27800000000000002</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="3">
         <v>0.25800000000000001</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <v>0.253</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <v>0.247</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="3">
         <v>0.248</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <v>0.251</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="3">
         <v>0.28499999999999998</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="3">
         <v>0.27400000000000002</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="3">
         <v>0.26700000000000002</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="3">
         <v>0.30399999999999999</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="3">
         <v>0.29899999999999999</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="3">
         <v>0.30399999999999999</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="3">
         <v>0.30299999999999999</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="3">
         <v>0.29699999999999999</v>
       </c>
-      <c r="R45">
+      <c r="R45" s="3">
         <v>0.29199999999999998</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="3">
         <v>0.26900000000000002</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="3">
         <v>0.26600000000000001</v>
       </c>
-      <c r="U45">
+      <c r="U45" s="3">
         <v>0.27800000000000002</v>
       </c>
-      <c r="V45">
+      <c r="V45" s="3">
         <v>0.28799999999999998</v>
       </c>
-      <c r="W45">
+      <c r="W45" s="3">
         <v>0.32300000000000001</v>
       </c>
-      <c r="X45">
+      <c r="X45" s="3">
         <v>0.38</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" s="3">
         <v>0.34</v>
       </c>
-      <c r="Z45">
+      <c r="Z45" s="3">
         <v>0.22</v>
       </c>
-      <c r="AA45">
+      <c r="AA45" s="3">
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="46" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="3">
         <v>1.2110000000000001</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="3">
         <v>1.1719999999999999</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="3">
         <v>1.0640000000000001</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="3">
         <v>1.0289999999999999</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="3">
         <v>1.087</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="3">
         <v>1.06</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="3">
         <v>1.1060000000000001</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="3">
         <v>1.125</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="3">
         <v>1.1870000000000001</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="3">
         <v>1.2270000000000001</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="3">
         <v>1.181</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="3">
         <v>1.1890000000000001</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="3">
         <v>1.1639999999999999</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="3">
         <v>1.1220000000000001</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="3">
         <v>1.135</v>
       </c>
-      <c r="R46">
+      <c r="R46" s="3">
         <v>1.0860000000000001</v>
       </c>
-      <c r="S46">
+      <c r="S46" s="3">
         <v>1.153</v>
       </c>
-      <c r="T46">
+      <c r="T46" s="3">
         <v>1.113</v>
       </c>
-      <c r="U46">
+      <c r="U46" s="3">
         <v>1.274</v>
       </c>
-      <c r="V46">
+      <c r="V46" s="3">
         <v>1.105</v>
       </c>
-      <c r="W46">
+      <c r="W46" s="3">
         <v>0.77700000000000002</v>
       </c>
-      <c r="X46">
+      <c r="X46" s="3">
         <v>0.78500000000000003</v>
       </c>
-      <c r="Y46">
+      <c r="Y46" s="3">
         <v>1.071</v>
       </c>
-      <c r="Z46">
+      <c r="Z46" s="3">
         <v>1.468</v>
       </c>
-      <c r="AA46">
+      <c r="AA46" s="3">
         <v>1.4850000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+    <row r="47" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="3">
         <v>6.0190000000000001</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="3">
         <v>5.9429999999999996</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="3">
         <v>5.8719999999999999</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="3">
         <v>5.7329999999999997</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <v>5.6369999999999996</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="3">
         <v>5.5519999999999996</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="3">
         <v>5.6470000000000002</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="3">
         <v>5.7409999999999997</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="3">
         <v>6.4370000000000003</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="3">
         <v>6.2930000000000001</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="3">
         <v>6.0439999999999996</v>
       </c>
-      <c r="N47">
+      <c r="N47" s="3">
         <v>5.99</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="3">
         <v>5.7930000000000001</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="3">
         <v>5.75</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="3">
         <v>5.734</v>
       </c>
-      <c r="R47">
+      <c r="R47" s="3">
         <v>5.6630000000000003</v>
       </c>
-      <c r="S47">
+      <c r="S47" s="3">
         <v>5.7370000000000001</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="3">
         <v>5.694</v>
       </c>
-      <c r="U47">
+      <c r="U47" s="3">
         <v>5.8209999999999997</v>
       </c>
-      <c r="V47">
+      <c r="V47" s="3">
         <v>5.7969999999999997</v>
       </c>
-      <c r="W47">
+      <c r="W47" s="3">
         <v>5.1079999999999997</v>
       </c>
-      <c r="X47">
+      <c r="X47" s="3">
         <v>5.3849999999999998</v>
       </c>
-      <c r="Y47">
+      <c r="Y47" s="3">
         <v>5.3070000000000004</v>
       </c>
-      <c r="Z47">
+      <c r="Z47" s="3">
         <v>5.2919999999999998</v>
       </c>
-      <c r="AA47">
+      <c r="AA47" s="3">
         <v>5.1369999999999996</v>
       </c>
     </row>
@@ -9511,86 +9499,86 @@
         <v>0.14099999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="59" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="3">
         <v>0.35299999999999998</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="3">
         <v>0.36399999999999999</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="3">
         <v>0.38500000000000001</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="3">
         <v>0.38700000000000001</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <v>0.375</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="3">
         <v>0.36899999999999999</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="3">
         <v>0.32500000000000001</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="3">
         <v>0.33300000000000002</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="3">
         <v>0.34699999999999998</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="3">
         <v>0.34899999999999998</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="3">
         <v>0.34799999999999998</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="3">
         <v>0.35399999999999998</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="3">
         <v>0.35799999999999998</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="3">
         <v>0.375</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="3">
         <v>0.35</v>
       </c>
-      <c r="R59">
+      <c r="R59" s="3">
         <v>0.34300000000000003</v>
       </c>
-      <c r="S59">
+      <c r="S59" s="3">
         <v>0.375</v>
       </c>
-      <c r="T59">
+      <c r="T59" s="3">
         <v>0.375</v>
       </c>
-      <c r="U59">
+      <c r="U59" s="3">
         <v>0.371</v>
       </c>
-      <c r="V59">
+      <c r="V59" s="3">
         <v>0.36599999999999999</v>
       </c>
-      <c r="W59">
+      <c r="W59" s="3">
         <v>0.38300000000000001</v>
       </c>
-      <c r="X59">
+      <c r="X59" s="3">
         <v>0.376</v>
       </c>
-      <c r="Y59">
+      <c r="Y59" s="3">
         <v>0.41299999999999998</v>
       </c>
-      <c r="Z59">
+      <c r="Z59" s="3">
         <v>0.41</v>
       </c>
-      <c r="AA59">
+      <c r="AA59" s="3">
         <v>0.29199999999999998</v>
       </c>
     </row>
@@ -10035,11 +10023,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA63" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA63">
-      <sortCondition ref="B1:B63"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>